--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Family_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Family_by_Sample_Layer.xlsx
@@ -712,10 +712,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>22.0698890283973</v>
+        <v>22.07717672444</v>
       </c>
       <c r="D2" t="n">
-        <v>1.17872018799861</v>
+        <v>1.17929120251656</v>
       </c>
     </row>
     <row r="3">
@@ -726,10 +726,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>17.4383623802787</v>
+        <v>17.4335608237773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.57404082297464</v>
+        <v>0.573903827456795</v>
       </c>
     </row>
     <row r="4">
@@ -740,10 +740,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>17.3894839929906</v>
+        <v>17.3856622419682</v>
       </c>
       <c r="D4" t="n">
-        <v>1.78427516910463</v>
+        <v>1.78393921753448</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>8.36211780916747</v>
+        <v>8.36354044156639</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8880237394107</v>
+        <v>1.88837296899669</v>
       </c>
     </row>
     <row r="6">
@@ -768,10 +768,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>6.37829834931532</v>
+        <v>6.37743089234223</v>
       </c>
       <c r="D6" t="n">
-        <v>0.201632562265746</v>
+        <v>0.201584535645552</v>
       </c>
     </row>
     <row r="7">
@@ -782,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>6.0952094129783</v>
+        <v>6.09481794786706</v>
       </c>
       <c r="D7"/>
     </row>
@@ -794,10 +794,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>4.25143439851143</v>
+        <v>4.25307457523083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.84736091756479</v>
+        <v>0.847691932907289</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>3.89590829939837</v>
+        <v>3.89737083936768</v>
       </c>
       <c r="D9" t="n">
-        <v>0.564837137137758</v>
+        <v>0.565051445211636</v>
       </c>
     </row>
     <row r="10">
@@ -822,10 +822,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>3.22608947813918</v>
+        <v>3.22543327786321</v>
       </c>
       <c r="D10" t="n">
-        <v>0.652462783436685</v>
+        <v>0.65231206138855</v>
       </c>
     </row>
     <row r="11">
@@ -836,10 +836,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>2.61567542300022</v>
+        <v>2.61572166037823</v>
       </c>
       <c r="D11" t="n">
-        <v>0.266309172716062</v>
+        <v>0.266328161330401</v>
       </c>
     </row>
     <row r="12">
@@ -850,10 +850,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>2.12221346618614</v>
+        <v>2.12151181288669</v>
       </c>
       <c r="D12" t="n">
-        <v>0.588657670421057</v>
+        <v>0.588465550326627</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>1.27604330034489</v>
+        <v>1.27570358577485</v>
       </c>
       <c r="D13" t="n">
-        <v>0.286174586870707</v>
+        <v>0.286113399427014</v>
       </c>
     </row>
     <row r="14">
@@ -878,10 +878,10 @@
         <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>0.98483464546458</v>
+        <v>0.984493672178256</v>
       </c>
       <c r="D14" t="n">
-        <v>0.41693837682382</v>
+        <v>0.416794022795259</v>
       </c>
     </row>
     <row r="15">
@@ -892,10 +892,10 @@
         <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>0.845107592204552</v>
+        <v>0.84517366263882</v>
       </c>
       <c r="D15" t="n">
-        <v>0.323352480859629</v>
+        <v>0.323376546012074</v>
       </c>
     </row>
     <row r="16">
@@ -906,10 +906,10 @@
         <v>41</v>
       </c>
       <c r="C16" t="n">
-        <v>0.842819608971247</v>
+        <v>0.843016143430554</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0557464320292799</v>
+        <v>0.0557795981523561</v>
       </c>
     </row>
     <row r="17">
@@ -920,10 +920,10 @@
         <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>0.564474994923797</v>
+        <v>0.564279560192745</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0340832466395912</v>
+        <v>0.0340714462052048</v>
       </c>
     </row>
     <row r="18">
@@ -934,10 +934,10 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>0.528587605318643</v>
+        <v>0.528564616265621</v>
       </c>
       <c r="D18" t="n">
-        <v>0.155918437664913</v>
+        <v>0.155860553194976</v>
       </c>
     </row>
     <row r="19">
@@ -948,10 +948,10 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>0.346145091863355</v>
+        <v>0.346314940638425</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0399684363248702</v>
+        <v>0.0399880491030856</v>
       </c>
     </row>
     <row r="20">
@@ -962,10 +962,10 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>0.198168603278418</v>
+        <v>0.198099992572837</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0102348477225202</v>
+        <v>0.0102313041736828</v>
       </c>
     </row>
     <row r="21">
@@ -976,10 +976,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>0.150868896821975</v>
+        <v>0.150844252164665</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0156795106512313</v>
+        <v>0.0156700114403627</v>
       </c>
     </row>
     <row r="22">
@@ -990,10 +990,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.144123624177585</v>
+        <v>0.144073725135143</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0849243589434293</v>
+        <v>0.0848949561011439</v>
       </c>
     </row>
     <row r="23">
@@ -1004,7 +1004,7 @@
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0.125162894608455</v>
+        <v>0.125138873055433</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1016,10 +1016,10 @@
         <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0889305135628142</v>
+        <v>0.0889659391173463</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0193712470556227</v>
+        <v>0.0193723438294962</v>
       </c>
     </row>
     <row r="25">
@@ -1030,7 +1030,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1042,7 +1042,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1079,10 +1079,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>23.208697606913</v>
+        <v>23.207771839438</v>
       </c>
       <c r="D2" t="n">
-        <v>1.20734204165949</v>
+        <v>1.20719583557395</v>
       </c>
     </row>
     <row r="3">
@@ -1093,10 +1093,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>18.7585675464447</v>
+        <v>18.7596754229218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.445227623743765</v>
+        <v>0.445256521377909</v>
       </c>
     </row>
     <row r="4">
@@ -1107,10 +1107,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>15.4088131875933</v>
+        <v>15.4088719795948</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7345361992899</v>
+        <v>10.7344944659556</v>
       </c>
     </row>
     <row r="5">
@@ -1121,10 +1121,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>8.27218139624052</v>
+        <v>8.27101045526418</v>
       </c>
       <c r="D5" t="n">
-        <v>1.36968109620548</v>
+        <v>1.36954730085311</v>
       </c>
     </row>
     <row r="6">
@@ -1135,10 +1135,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>5.75200313986558</v>
+        <v>5.75290790518388</v>
       </c>
       <c r="D6" t="n">
-        <v>1.01899653575214</v>
+        <v>1.01917258605361</v>
       </c>
     </row>
     <row r="7">
@@ -1149,10 +1149,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.68965562659846</v>
+        <v>5.69001356082827</v>
       </c>
       <c r="D7" t="n">
-        <v>0.104055190092079</v>
+        <v>0.104069088706042</v>
       </c>
     </row>
     <row r="8">
@@ -1163,10 +1163,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>5.50235662250732</v>
+        <v>5.50252043016617</v>
       </c>
       <c r="D8" t="n">
-        <v>0.800444125543568</v>
+        <v>0.80046181295353</v>
       </c>
     </row>
     <row r="9">
@@ -1177,10 +1177,10 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>4.01645242788765</v>
+        <v>4.01579072395459</v>
       </c>
       <c r="D9" t="n">
-        <v>1.90474767622298</v>
+        <v>1.90442337340355</v>
       </c>
     </row>
     <row r="10">
@@ -1191,10 +1191,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8326121058502</v>
+        <v>2.83259050834335</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0375308611696348</v>
+        <v>0.0375284299568896</v>
       </c>
     </row>
     <row r="11">
@@ -1205,10 +1205,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>2.72315175441127</v>
+        <v>2.72301279020991</v>
       </c>
       <c r="D11" t="n">
-        <v>0.119683381183223</v>
+        <v>0.119670820428728</v>
       </c>
     </row>
     <row r="12">
@@ -1219,10 +1219,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>1.73603927064758</v>
+        <v>1.73634246894241</v>
       </c>
       <c r="D12" t="n">
-        <v>0.137986526107818</v>
+        <v>0.138006835212184</v>
       </c>
     </row>
     <row r="13">
@@ -1233,10 +1233,10 @@
         <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>1.58574655495638</v>
+        <v>1.5857200763407</v>
       </c>
       <c r="D13" t="n">
-        <v>0.149916665967348</v>
+        <v>0.149933979851808</v>
       </c>
     </row>
     <row r="14">
@@ -1247,10 +1247,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1313777084094</v>
+        <v>1.13107877908915</v>
       </c>
       <c r="D14" t="n">
-        <v>0.438306876347372</v>
+        <v>0.438166274567279</v>
       </c>
     </row>
     <row r="15">
@@ -1261,10 +1261,10 @@
         <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>0.533191579369875</v>
+        <v>0.533244440897158</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0473778828666499</v>
+        <v>0.0473843566599068</v>
       </c>
     </row>
     <row r="16">
@@ -1275,10 +1275,10 @@
         <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>0.468229522913405</v>
+        <v>0.468371564862802</v>
       </c>
       <c r="D16" t="n">
-        <v>0.149165523530978</v>
+        <v>0.149207377552987</v>
       </c>
     </row>
     <row r="17">
@@ -1289,10 +1289,10 @@
         <v>35</v>
       </c>
       <c r="C17" t="n">
-        <v>0.383746008165241</v>
+        <v>0.383770199738571</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0758668893468855</v>
+        <v>0.0758476664213962</v>
       </c>
     </row>
     <row r="18">
@@ -1303,10 +1303,10 @@
         <v>46</v>
       </c>
       <c r="C18" t="n">
-        <v>0.335446007240345</v>
+        <v>0.335502608919009</v>
       </c>
       <c r="D18" t="n">
-        <v>0.145391150819068</v>
+        <v>0.145399331381891</v>
       </c>
     </row>
     <row r="19">
@@ -1317,10 +1317,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>0.327482849066667</v>
+        <v>0.327415679613048</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0352004257476803</v>
+        <v>0.035190434385075</v>
       </c>
     </row>
     <row r="20">
@@ -1331,10 +1331,10 @@
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>0.313011764481159</v>
+        <v>0.313003479629514</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0264669082796906</v>
+        <v>0.0264561600207882</v>
       </c>
     </row>
     <row r="21">
@@ -1345,10 +1345,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.273902700999505</v>
+        <v>0.274042873992849</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0485332336861192</v>
+        <v>0.0485576809991882</v>
       </c>
     </row>
     <row r="22">
@@ -1359,10 +1359,10 @@
         <v>30</v>
       </c>
       <c r="C22" t="n">
-        <v>0.253850907049785</v>
+        <v>0.253812213615222</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07776340641984</v>
+        <v>0.0777507059732587</v>
       </c>
     </row>
     <row r="23">
@@ -1373,10 +1373,10 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>0.164086084687455</v>
+        <v>0.164103314192489</v>
       </c>
       <c r="D23" t="n">
-        <v>0.100158054529747</v>
+        <v>0.100180123502046</v>
       </c>
     </row>
     <row r="24">
@@ -1387,7 +1387,7 @@
         <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>0.152516179850445</v>
+        <v>0.152530179595588</v>
       </c>
       <c r="D24"/>
     </row>
@@ -1399,10 +1399,10 @@
         <v>41</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0980842454091233</v>
+        <v>0.0980799672171447</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0230756382404663</v>
+        <v>0.0230733844377137</v>
       </c>
     </row>
     <row r="26">
@@ -1413,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0437381858883574</v>
+        <v>0.0437387712383516</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1425,7 +1425,7 @@
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0197210594583907</v>
+        <v>0.0197308085877413</v>
       </c>
       <c r="D27"/>
     </row>
@@ -1437,7 +1437,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00657407331009671</v>
+        <v>0.00657693619591377</v>
       </c>
       <c r="D28"/>
     </row>
@@ -1449,7 +1449,7 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D29"/>
     </row>
@@ -1461,7 +1461,7 @@
         <v>37</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D30"/>
     </row>
@@ -1933,10 +1933,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6421608383319</v>
+        <v>24.6417854302772</v>
       </c>
       <c r="D2" t="n">
-        <v>4.50858756758852</v>
+        <v>4.50850291956916</v>
       </c>
     </row>
     <row r="3">
@@ -1947,10 +1947,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>21.9561628285138</v>
+        <v>21.9557849726509</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16771398525829</v>
+        <v>1.16769782773181</v>
       </c>
     </row>
     <row r="4">
@@ -1961,10 +1961,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2655397706116</v>
+        <v>19.2658310749008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.801037083083817</v>
+        <v>0.801053720061133</v>
       </c>
     </row>
     <row r="5">
@@ -1975,10 +1975,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8557823044562</v>
+        <v>5.85590244379546</v>
       </c>
       <c r="D5" t="n">
-        <v>0.163137066026689</v>
+        <v>0.163138527581659</v>
       </c>
     </row>
     <row r="6">
@@ -1989,10 +1989,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>5.64193695488102</v>
+        <v>5.64180376429859</v>
       </c>
       <c r="D6" t="n">
-        <v>1.11225319868185</v>
+        <v>1.11217301857517</v>
       </c>
     </row>
     <row r="7">
@@ -2003,10 +2003,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>5.54204949466641</v>
+        <v>5.5422000955275</v>
       </c>
       <c r="D7" t="n">
-        <v>1.05968322937623</v>
+        <v>1.05970997848961</v>
       </c>
     </row>
     <row r="8">
@@ -2017,10 +2017,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>3.93840198783546</v>
+        <v>3.93853124820496</v>
       </c>
       <c r="D8" t="n">
-        <v>2.37820589277897</v>
+        <v>2.37830413975467</v>
       </c>
     </row>
     <row r="9">
@@ -2031,10 +2031,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>2.68983581567514</v>
+        <v>2.68972901058529</v>
       </c>
       <c r="D9" t="n">
-        <v>0.324633621661211</v>
+        <v>0.324586081290426</v>
       </c>
     </row>
     <row r="10">
@@ -2045,10 +2045,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2.11425113709016</v>
+        <v>2.11456979523719</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0630137464579822</v>
+        <v>0.0630184558174494</v>
       </c>
     </row>
     <row r="11">
@@ -2059,10 +2059,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>1.64273042181408</v>
+        <v>1.64289298050545</v>
       </c>
       <c r="D11" t="n">
-        <v>0.024766852070001</v>
+        <v>0.0247685597634855</v>
       </c>
     </row>
     <row r="12">
@@ -2073,10 +2073,10 @@
         <v>46</v>
       </c>
       <c r="C12" t="n">
-        <v>1.14667551612367</v>
+        <v>1.1465334653637</v>
       </c>
       <c r="D12" t="n">
-        <v>0.369766800613695</v>
+        <v>0.36969012059224</v>
       </c>
     </row>
     <row r="13">
@@ -2087,10 +2087,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.956395560811265</v>
+        <v>0.956500761814801</v>
       </c>
       <c r="D13" t="n">
-        <v>0.101961225414945</v>
+        <v>0.101967492441141</v>
       </c>
     </row>
     <row r="14">
@@ -2101,10 +2101,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>0.834037369701974</v>
+        <v>0.834029498868685</v>
       </c>
       <c r="D14" t="n">
-        <v>0.580609513304316</v>
+        <v>0.580609968111834</v>
       </c>
     </row>
     <row r="15">
@@ -2115,10 +2115,10 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>0.580951198999283</v>
+        <v>0.580955967893585</v>
       </c>
       <c r="D15" t="n">
-        <v>0.159803789662683</v>
+        <v>0.15980181421233</v>
       </c>
     </row>
     <row r="16">
@@ -2129,7 +2129,7 @@
         <v>54</v>
       </c>
       <c r="C16" t="n">
-        <v>0.561396773370258</v>
+        <v>0.561284058446422</v>
       </c>
       <c r="D16"/>
     </row>
@@ -2141,10 +2141,10 @@
         <v>38</v>
       </c>
       <c r="C17" t="n">
-        <v>0.509147384705421</v>
+        <v>0.509037052599851</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1146841955465</v>
+        <v>0.114665641911313</v>
       </c>
     </row>
     <row r="18">
@@ -2155,10 +2155,10 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>0.407956245260099</v>
+        <v>0.407987245009878</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04072813612845</v>
+        <v>0.0407363638337707</v>
       </c>
     </row>
     <row r="19">
@@ -2169,10 +2169,10 @@
         <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>0.40384000586343</v>
+        <v>0.403805868403884</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0840527736502546</v>
+        <v>0.0840541885700224</v>
       </c>
     </row>
     <row r="20">
@@ -2183,10 +2183,10 @@
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>0.249306340048411</v>
+        <v>0.249311435523764</v>
       </c>
       <c r="D20" t="n">
-        <v>0.026880090038289</v>
+        <v>0.0268774857163241</v>
       </c>
     </row>
     <row r="21">
@@ -2197,10 +2197,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.228057665401595</v>
+        <v>0.228083611828135</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0108421662300314</v>
+        <v>0.0108436106215398</v>
       </c>
     </row>
     <row r="22">
@@ -2211,7 +2211,7 @@
         <v>32</v>
       </c>
       <c r="C22" t="n">
-        <v>0.222556886622985</v>
+        <v>0.22251479576491</v>
       </c>
       <c r="D22"/>
     </row>
@@ -2223,10 +2223,10 @@
         <v>24</v>
       </c>
       <c r="C23" t="n">
-        <v>0.167099028183799</v>
+        <v>0.167151387445175</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00960303150393894</v>
+        <v>0.00960494096614654</v>
       </c>
     </row>
     <row r="24">
@@ -2237,7 +2237,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0794954454718848</v>
+        <v>0.0794804603356408</v>
       </c>
       <c r="D24"/>
     </row>
@@ -2249,10 +2249,10 @@
         <v>21</v>
       </c>
       <c r="C25" t="n">
-        <v>0.074254792274124</v>
+        <v>0.0742539301604906</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0189524110839475</v>
+        <v>0.0189479555191827</v>
       </c>
     </row>
     <row r="26">
@@ -2263,10 +2263,10 @@
         <v>41</v>
       </c>
       <c r="C26" t="n">
-        <v>0.063016756916131</v>
+        <v>0.0630217691918993</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0106182411349641</v>
+        <v>0.0106206001393996</v>
       </c>
     </row>
     <row r="27">
@@ -2277,10 +2277,10 @@
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0542304623700162</v>
+        <v>0.0542595553889274</v>
       </c>
       <c r="D27" t="n">
-        <v>0.011559847004357</v>
+        <v>0.0115623328292755</v>
       </c>
     </row>
     <row r="28">
@@ -2291,10 +2291,10 @@
         <v>30</v>
       </c>
       <c r="C28" t="n">
-        <v>0.051623866740213</v>
+        <v>0.0516379046782591</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0104755880492871</v>
+        <v>0.0104789957127142</v>
       </c>
     </row>
     <row r="29">
@@ -2305,10 +2305,10 @@
         <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0330077239981236</v>
+        <v>0.033012673458996</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0187680021831362</v>
+        <v>0.0187745121440375</v>
       </c>
     </row>
     <row r="30">
@@ -2319,7 +2319,7 @@
         <v>47</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0286275448625279</v>
+        <v>0.0286216562756727</v>
       </c>
       <c r="D30"/>
     </row>
@@ -2331,10 +2331,10 @@
         <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0256296166140272</v>
+        <v>0.0256188408789521</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0052826036674671</v>
+        <v>0.00527685889155468</v>
       </c>
     </row>
     <row r="32">
@@ -2345,7 +2345,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0215354993342044</v>
+        <v>0.0215518136787733</v>
       </c>
       <c r="D32"/>
     </row>
@@ -2357,7 +2357,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00769163117802357</v>
+        <v>0.00769723967014162</v>
       </c>
       <c r="D33"/>
     </row>
@@ -2369,7 +2369,7 @@
         <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="D34"/>
     </row>
@@ -2406,10 +2406,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>21.2485385492539</v>
+        <v>21.2458563989728</v>
       </c>
       <c r="D2" t="n">
-        <v>1.22320616283503</v>
+        <v>1.22297045627264</v>
       </c>
     </row>
     <row r="3">
@@ -2420,10 +2420,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>19.8741580235539</v>
+        <v>19.8722980417864</v>
       </c>
       <c r="D3" t="n">
-        <v>1.08247297210186</v>
+        <v>1.08232234927472</v>
       </c>
     </row>
     <row r="4">
@@ -2434,10 +2434,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>17.7241798195007</v>
+        <v>17.7224537820169</v>
       </c>
       <c r="D4" t="n">
-        <v>4.54736451659128</v>
+        <v>4.54672531155237</v>
       </c>
     </row>
     <row r="5">
@@ -2448,10 +2448,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5118933543116</v>
+        <v>12.5158221148857</v>
       </c>
       <c r="D5" t="n">
-        <v>4.84513813620268</v>
+        <v>4.84664378215444</v>
       </c>
     </row>
     <row r="6">
@@ -2462,10 +2462,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>10.6290535606668</v>
+        <v>10.6283808772554</v>
       </c>
       <c r="D6" t="n">
-        <v>5.72148293638644</v>
+        <v>5.72085521364488</v>
       </c>
     </row>
     <row r="7">
@@ -2476,7 +2476,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5.12700882116796</v>
+        <v>5.12663012137111</v>
       </c>
       <c r="D7"/>
     </row>
@@ -2488,10 +2488,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5410657193669</v>
+        <v>4.54254025821407</v>
       </c>
       <c r="D8" t="n">
-        <v>1.26372211027965</v>
+        <v>1.26424553476954</v>
       </c>
     </row>
     <row r="9">
@@ -2502,10 +2502,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>3.42924529730402</v>
+        <v>3.4306325226418</v>
       </c>
       <c r="D9" t="n">
-        <v>1.30875082780457</v>
+        <v>1.30926703969254</v>
       </c>
     </row>
     <row r="10">
@@ -2516,10 +2516,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>1.21751116830729</v>
+        <v>1.2177090508129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.489497778370004</v>
+        <v>0.489615016945174</v>
       </c>
     </row>
     <row r="11">
@@ -2530,10 +2530,10 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>1.09845515103157</v>
+        <v>1.09861161623602</v>
       </c>
       <c r="D11" t="n">
-        <v>0.259735777881981</v>
+        <v>0.259767490523437</v>
       </c>
     </row>
     <row r="12">
@@ -2544,10 +2544,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0764610187463</v>
+        <v>1.07669850745551</v>
       </c>
       <c r="D12" t="n">
-        <v>0.186974950143159</v>
+        <v>0.18702418051521</v>
       </c>
     </row>
     <row r="13">
@@ -2558,10 +2558,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>0.884332464167625</v>
+        <v>0.884219761323417</v>
       </c>
       <c r="D13" t="n">
-        <v>0.194272206822491</v>
+        <v>0.194232486563927</v>
       </c>
     </row>
     <row r="14">
@@ -2572,10 +2572,10 @@
         <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.272068552038335</v>
+        <v>0.272095187481516</v>
       </c>
       <c r="D14" t="n">
-        <v>0.112442581800846</v>
+        <v>0.112472967401727</v>
       </c>
     </row>
     <row r="15">
@@ -2586,7 +2586,7 @@
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>0.106510209713172</v>
+        <v>0.106529229357992</v>
       </c>
       <c r="D15"/>
     </row>
@@ -2598,7 +2598,7 @@
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0745489076284746</v>
+        <v>0.0745232685650044</v>
       </c>
       <c r="D16"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0715961669774393</v>
+        <v>0.0716027079473664</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00208790293743219</v>
+        <v>0.00206514821759822</v>
       </c>
     </row>
     <row r="18">
@@ -2624,7 +2624,7 @@
         <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.048049953067902</v>
+        <v>0.0480779483382211</v>
       </c>
       <c r="D18"/>
     </row>
@@ -2636,7 +2636,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0447297899376656</v>
+        <v>0.0447144063464139</v>
       </c>
       <c r="D19"/>
     </row>
@@ -2648,7 +2648,7 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0205934732585021</v>
+        <v>0.0206041989915073</v>
       </c>
       <c r="D20"/>
     </row>
@@ -2685,10 +2685,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>56.2950113123006</v>
+        <v>56.3041081219849</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8490255669441</v>
+        <v>13.856182263946</v>
       </c>
     </row>
     <row r="3">
@@ -2699,10 +2699,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0508572343531</v>
+        <v>17.0352886501756</v>
       </c>
       <c r="D3" t="n">
-        <v>4.68457221441722</v>
+        <v>4.67777158284229</v>
       </c>
     </row>
     <row r="4">
@@ -2713,10 +2713,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8.97414045002143</v>
+        <v>8.97376302770651</v>
       </c>
       <c r="D4" t="n">
-        <v>2.23722456511995</v>
+        <v>2.23691437036538</v>
       </c>
     </row>
     <row r="5">
@@ -2727,10 +2727,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>4.65985259507985</v>
+        <v>4.66228845333324</v>
       </c>
       <c r="D5" t="n">
-        <v>3.20270178727532</v>
+        <v>3.20458350215252</v>
       </c>
     </row>
     <row r="6">
@@ -2741,10 +2741,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.95563362159775</v>
+        <v>2.95631754482207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.166350486782069</v>
+        <v>0.166443705551338</v>
       </c>
     </row>
     <row r="7">
@@ -2755,10 +2755,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.92746868843593</v>
+        <v>2.92799332344778</v>
       </c>
       <c r="D7" t="n">
-        <v>0.114129339263368</v>
+        <v>0.114145615268467</v>
       </c>
     </row>
     <row r="8">
@@ -2769,10 +2769,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>2.07571960745581</v>
+        <v>2.07617088760931</v>
       </c>
       <c r="D8" t="n">
-        <v>0.495033498552083</v>
+        <v>0.495069019223064</v>
       </c>
     </row>
     <row r="9">
@@ -2783,10 +2783,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>1.98068645471414</v>
+        <v>1.98260103785225</v>
       </c>
       <c r="D9" t="n">
-        <v>0.40990712214849</v>
+        <v>0.410246235998562</v>
       </c>
     </row>
     <row r="10">
@@ -2797,10 +2797,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.967041921835672</v>
+        <v>0.967424695406141</v>
       </c>
       <c r="D10" t="n">
-        <v>0.137633057761389</v>
+        <v>0.137743280417042</v>
       </c>
     </row>
     <row r="11">
@@ -2811,10 +2811,10 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>0.653944782403579</v>
+        <v>0.653790508001574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.133944302900671</v>
+        <v>0.133970579529824</v>
       </c>
     </row>
     <row r="12">
@@ -2825,10 +2825,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.42055134000046</v>
+        <v>0.420978721028352</v>
       </c>
       <c r="D12" t="n">
-        <v>0.251217866740883</v>
+        <v>0.251600768850808</v>
       </c>
     </row>
     <row r="13">
@@ -2839,10 +2839,10 @@
         <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>0.294797111390009</v>
+        <v>0.294801554152728</v>
       </c>
       <c r="D13" t="n">
-        <v>0.060127286461208</v>
+        <v>0.0601038972054638</v>
       </c>
     </row>
     <row r="14">
@@ -2853,7 +2853,7 @@
         <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>0.273245290917606</v>
+        <v>0.273220773321349</v>
       </c>
       <c r="D14"/>
     </row>
@@ -2865,10 +2865,10 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>0.146706606236118</v>
+        <v>0.146671676698119</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0305908622402212</v>
+        <v>0.0304749569700577</v>
       </c>
     </row>
     <row r="16">
@@ -2879,10 +2879,10 @@
         <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>0.110220518298119</v>
+        <v>0.110260935136766</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0450243073135336</v>
+        <v>0.0450239683206631</v>
       </c>
     </row>
     <row r="17">
@@ -2893,10 +2893,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0905129096455505</v>
+        <v>0.0906268818335357</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0213347951269941</v>
+        <v>0.0213609609007617</v>
       </c>
     </row>
     <row r="18">
@@ -2907,7 +2907,7 @@
         <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0374081938479166</v>
+        <v>0.0373818914578821</v>
       </c>
       <c r="D18"/>
     </row>
@@ -2919,7 +2919,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0344805445865737</v>
+        <v>0.0345245264127755</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2933,10 +2933,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.030170476513252</v>
+        <v>0.0302089606111786</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00304767836202143</v>
+        <v>0.00305156584296595</v>
       </c>
     </row>
     <row r="21">
@@ -2947,7 +2947,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0215503403666086</v>
+        <v>0.0215778290079847</v>
       </c>
       <c r="D21"/>
     </row>
@@ -2984,10 +2984,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>39.7281014519403</v>
+        <v>39.7290616830707</v>
       </c>
       <c r="D2" t="n">
-        <v>6.21860820764229</v>
+        <v>6.21835232915755</v>
       </c>
     </row>
     <row r="3">
@@ -2998,10 +2998,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8879985888077</v>
+        <v>34.8859603682263</v>
       </c>
       <c r="D3" t="n">
-        <v>4.42073812416722</v>
+        <v>4.42043960561398</v>
       </c>
     </row>
     <row r="4">
@@ -3012,10 +3012,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>7.53251208659025</v>
+        <v>7.53238581525108</v>
       </c>
       <c r="D4" t="n">
-        <v>0.237454364070223</v>
+        <v>0.237447338734724</v>
       </c>
     </row>
     <row r="5">
@@ -3026,10 +3026,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>5.91242411014396</v>
+        <v>5.91280287303072</v>
       </c>
       <c r="D5" t="n">
-        <v>0.512420520758894</v>
+        <v>0.51247295122876</v>
       </c>
     </row>
     <row r="6">
@@ -3040,10 +3040,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.44575576170417</v>
+        <v>4.44623453436161</v>
       </c>
       <c r="D6" t="n">
-        <v>0.630523071027679</v>
+        <v>0.63055259443331</v>
       </c>
     </row>
     <row r="7">
@@ -3054,10 +3054,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25694228270683</v>
+        <v>3.25710668864576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.70733559831466</v>
+        <v>0.707350658262006</v>
       </c>
     </row>
     <row r="8">
@@ -3068,7 +3068,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1.12314048822747</v>
+        <v>1.12319999181149</v>
       </c>
       <c r="D8"/>
     </row>
@@ -3080,7 +3080,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>0.918428526744664</v>
+        <v>0.918331540824173</v>
       </c>
       <c r="D9"/>
     </row>
@@ -3092,10 +3092,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.558108885552207</v>
+        <v>0.558162676090998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0461198226177086</v>
+        <v>0.0461237017220785</v>
       </c>
     </row>
     <row r="11">
@@ -3106,10 +3106,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.494833544322251</v>
+        <v>0.494917936870067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0431730031535043</v>
+        <v>0.043185765399925</v>
       </c>
     </row>
     <row r="12">
@@ -3120,10 +3120,10 @@
         <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2535018465008</v>
+        <v>0.253525157028426</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0546702359334213</v>
+        <v>0.0546684509143556</v>
       </c>
     </row>
     <row r="13">
@@ -3134,10 +3134,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>0.201017799609721</v>
+        <v>0.201066748336308</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0166007935472507</v>
+        <v>0.016605692705767</v>
       </c>
     </row>
     <row r="14">
@@ -3148,10 +3148,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.149049513109839</v>
+        <v>0.149076724973757</v>
       </c>
       <c r="D14" t="n">
-        <v>0.022773446583883</v>
+        <v>0.0227812590279868</v>
       </c>
     </row>
     <row r="15">
@@ -3162,10 +3162,10 @@
         <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>0.108401006922979</v>
+        <v>0.108387807070915</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0395979660187865</v>
+        <v>0.0395979486402563</v>
       </c>
     </row>
     <row r="16">
@@ -3176,7 +3176,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0846707889820255</v>
+        <v>0.0846647635257898</v>
       </c>
       <c r="D16"/>
     </row>
@@ -3188,7 +3188,7 @@
         <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0603012976389215</v>
+        <v>0.0603064817301813</v>
       </c>
       <c r="D17"/>
     </row>
@@ -3200,10 +3200,10 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0500354950193752</v>
+        <v>0.0500356743516428</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0267642568796029</v>
+        <v>0.0267683469819272</v>
       </c>
     </row>
     <row r="19">
@@ -3214,10 +3214,10 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0433029130768202</v>
+        <v>0.0433099303780374</v>
       </c>
       <c r="D19" t="n">
-        <v>0.011123392364013</v>
+        <v>0.0111281360177655</v>
       </c>
     </row>
     <row r="20">
@@ -3228,10 +3228,10 @@
         <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0376415257929039</v>
+        <v>0.0376593776481822</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0129554095710758</v>
+        <v>0.0129613740499146</v>
       </c>
     </row>
     <row r="21">
@@ -3242,10 +3242,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0365553598602102</v>
+        <v>0.0365385450224773</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00406170665113446</v>
+        <v>0.00405983833583081</v>
       </c>
     </row>
     <row r="22">
@@ -3256,10 +3256,10 @@
         <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0268330144888622</v>
+        <v>0.0268281539567913</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00748556523992058</v>
+        <v>0.00748741271841554</v>
       </c>
     </row>
     <row r="23">
@@ -3270,7 +3270,7 @@
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>0.026401093232374</v>
+        <v>0.0263889491829003</v>
       </c>
       <c r="D23"/>
     </row>
@@ -3282,7 +3282,7 @@
         <v>36</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0222428218635845</v>
+        <v>0.0222527924706864</v>
       </c>
       <c r="D24"/>
     </row>
@@ -3294,10 +3294,10 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.014967531236534</v>
+        <v>0.0149666321842285</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00090459842985605</v>
+        <v>0.000899949762155514</v>
       </c>
     </row>
     <row r="26">
@@ -3308,7 +3308,7 @@
         <v>37</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="D26"/>
     </row>
@@ -3320,7 +3320,7 @@
         <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0060925599767017</v>
+        <v>0.00608975750374622</v>
       </c>
       <c r="D27"/>
     </row>
@@ -3332,7 +3332,7 @@
         <v>13</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00513290130977313</v>
+        <v>0.00513502957958107</v>
       </c>
       <c r="D28"/>
     </row>
@@ -3344,7 +3344,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00342168468528117</v>
+        <v>0.00342385186597158</v>
       </c>
       <c r="D29"/>
     </row>
@@ -3592,10 +3592,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>47.3349099499171</v>
+        <v>47.326281999477</v>
       </c>
       <c r="D2" t="n">
-        <v>0.965805550972033</v>
+        <v>0.965683214892171</v>
       </c>
     </row>
     <row r="3">
@@ -3606,10 +3606,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>22.4244649064651</v>
+        <v>22.425180009465</v>
       </c>
       <c r="D3" t="n">
-        <v>0.513727213121589</v>
+        <v>0.513840743555535</v>
       </c>
     </row>
     <row r="4">
@@ -3620,10 +3620,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>15.9046629771807</v>
+        <v>15.9133360695454</v>
       </c>
       <c r="D4" t="n">
-        <v>1.08475902120531</v>
+        <v>1.0856805763707</v>
       </c>
     </row>
     <row r="5">
@@ -3634,10 +3634,10 @@
         <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>4.29739103414817</v>
+        <v>4.2998423207784</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0933524972452613</v>
+        <v>0.0933985187150417</v>
       </c>
     </row>
     <row r="6">
@@ -3648,10 +3648,10 @@
         <v>42</v>
       </c>
       <c r="C6" t="n">
-        <v>3.50914346504936</v>
+        <v>3.50962344380878</v>
       </c>
       <c r="D6" t="n">
-        <v>0.207091168383744</v>
+        <v>0.207271608753574</v>
       </c>
     </row>
     <row r="7">
@@ -3662,10 +3662,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.57546103239077</v>
+        <v>2.57620868287384</v>
       </c>
       <c r="D7" t="n">
-        <v>0.234792745253268</v>
+        <v>0.234970077300637</v>
       </c>
     </row>
     <row r="8">
@@ -3676,10 +3676,10 @@
         <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>2.16668596383204</v>
+        <v>2.16443405405348</v>
       </c>
       <c r="D8" t="n">
-        <v>0.27519953695754</v>
+        <v>0.275025950300554</v>
       </c>
     </row>
     <row r="9">
@@ -3690,10 +3690,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.74281337850058</v>
+        <v>0.741563473474212</v>
       </c>
       <c r="D9" t="n">
-        <v>0.49049152785471</v>
+        <v>0.489687992578949</v>
       </c>
     </row>
     <row r="10">
@@ -3704,10 +3704,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>0.298005242007987</v>
+        <v>0.297697170490835</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0245469511332483</v>
+        <v>0.0245026224151622</v>
       </c>
     </row>
     <row r="11">
@@ -3718,10 +3718,10 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.233212573726985</v>
+        <v>0.23305415970703</v>
       </c>
       <c r="D11" t="n">
-        <v>0.111575935118184</v>
+        <v>0.111513697356389</v>
       </c>
     </row>
     <row r="12">
@@ -3732,7 +3732,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>0.219769260139959</v>
+        <v>0.219623369698133</v>
       </c>
       <c r="D12"/>
     </row>
@@ -3744,7 +3744,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>0.081013606389594</v>
+        <v>0.0810849869124129</v>
       </c>
       <c r="D13"/>
     </row>
@@ -3756,10 +3756,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0781988407569468</v>
+        <v>0.0780182178083647</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0103276745277303</v>
+        <v>0.0103038197620185</v>
       </c>
     </row>
     <row r="15">
@@ -3770,10 +3770,10 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0625588957431237</v>
+        <v>0.0624143977927732</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00844884085840169</v>
+        <v>0.00842932580506875</v>
       </c>
     </row>
     <row r="16">
@@ -3784,10 +3784,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0447621133500903</v>
+        <v>0.044693130754824</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0189029136531948</v>
+        <v>0.0188349213869587</v>
       </c>
     </row>
     <row r="17">
@@ -3798,10 +3798,10 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0224394212781726</v>
+        <v>0.02243082212351</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000681580412900505</v>
+        <v>0.0000985696922639011</v>
       </c>
     </row>
     <row r="18">
@@ -3812,7 +3812,7 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00450733912334368</v>
+        <v>0.00451369123599265</v>
       </c>
       <c r="D18"/>
     </row>
@@ -3849,10 +3849,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>57.3281405082253</v>
+        <v>57.3281477801791</v>
       </c>
       <c r="D2" t="n">
-        <v>40.3536957324513</v>
+        <v>40.3536922096008</v>
       </c>
     </row>
     <row r="3">
@@ -3863,7 +3863,7 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1608311737856</v>
+        <v>31.1608281680983</v>
       </c>
       <c r="D3"/>
     </row>
@@ -3875,7 +3875,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10635960191601</v>
+        <v>8.10635394396169</v>
       </c>
       <c r="D4"/>
     </row>
@@ -3887,7 +3887,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>2.98313940681246</v>
+        <v>2.98314090517806</v>
       </c>
       <c r="D5"/>
     </row>
@@ -3899,7 +3899,7 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>0.42152930926069</v>
+        <v>0.421529202582811</v>
       </c>
       <c r="D6"/>
     </row>
@@ -3936,10 +3936,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>94.0187702741291</v>
+        <v>94.0396963929599</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8363407254187</v>
+        <v>29.8417603709548</v>
       </c>
     </row>
     <row r="3">
@@ -3950,10 +3950,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>2.46890703144531</v>
+        <v>2.46278487288434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08710525321409</v>
+        <v>0.0870575126095609</v>
       </c>
     </row>
     <row r="4">
@@ -3964,10 +3964,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>0.760679645127287</v>
+        <v>0.759402820259848</v>
       </c>
       <c r="D4" t="n">
-        <v>0.116497598478017</v>
+        <v>0.116513645389048</v>
       </c>
     </row>
     <row r="5">
@@ -3978,10 +3978,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.662619659931421</v>
+        <v>0.658718649738598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0196785784858147</v>
+        <v>0.019562734423141</v>
       </c>
     </row>
     <row r="6">
@@ -3992,10 +3992,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>0.570724366816388</v>
+        <v>0.567713398141494</v>
       </c>
       <c r="D6" t="n">
-        <v>0.388472017279955</v>
+        <v>0.386431784779191</v>
       </c>
     </row>
     <row r="7">
@@ -4006,10 +4006,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.365483940765809</v>
+        <v>0.364752632660417</v>
       </c>
       <c r="D7" t="n">
-        <v>0.254843093468926</v>
+        <v>0.254346979051385</v>
       </c>
     </row>
     <row r="8">
@@ -4020,10 +4020,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>0.259661212468771</v>
+        <v>0.258132606660807</v>
       </c>
       <c r="D8" t="n">
-        <v>0.022324043078088</v>
+        <v>0.0221926573355361</v>
       </c>
     </row>
     <row r="9">
@@ -4034,10 +4034,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.199192433748206</v>
+        <v>0.198019888344106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0222951020193061</v>
+        <v>0.0221638051926366</v>
       </c>
     </row>
     <row r="10">
@@ -4048,10 +4048,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.190898338682771</v>
+        <v>0.190677332152804</v>
       </c>
       <c r="D10" t="n">
-        <v>0.064368226732903</v>
+        <v>0.0644377307378925</v>
       </c>
     </row>
     <row r="11">
@@ -4062,10 +4062,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.105694253405797</v>
+        <v>0.105071841369835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00655903092408336</v>
+        <v>0.00652037608813461</v>
       </c>
     </row>
     <row r="12">
@@ -4076,10 +4076,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0.103153142013586</v>
+        <v>0.102545998701173</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0101332058977902</v>
+        <v>0.0100735684974025</v>
       </c>
     </row>
     <row r="13">
@@ -4090,10 +4090,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0818111706369464</v>
+        <v>0.0813294628481086</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0110361643657286</v>
+        <v>0.0109712459676748</v>
       </c>
     </row>
     <row r="14">
@@ -4104,10 +4104,10 @@
         <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0564040518423816</v>
+        <v>0.056071870874866</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00495065092088728</v>
+        <v>0.00492150097575072</v>
       </c>
     </row>
     <row r="15">
@@ -4118,10 +4118,10 @@
         <v>41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0320131673348304</v>
+        <v>0.031824490762082</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00288790137493388</v>
+        <v>0.00287098879932759</v>
       </c>
     </row>
     <row r="16">
@@ -4132,10 +4132,10 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0315049450563881</v>
+        <v>0.0313196978493678</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00421072009354453</v>
+        <v>0.00418595584490087</v>
       </c>
     </row>
     <row r="17">
@@ -4146,10 +4146,10 @@
         <v>46</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02388287249898</v>
+        <v>0.023742169843383</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00467103303641761</v>
+        <v>0.00464364622282581</v>
       </c>
     </row>
     <row r="18">
@@ -4160,10 +4160,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0213419713766395</v>
+        <v>0.0212165358530648</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00881592715433516</v>
+        <v>0.00876410834067219</v>
       </c>
     </row>
     <row r="19">
@@ -4174,7 +4174,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0116872199753333</v>
+        <v>0.0116185841261627</v>
       </c>
       <c r="D19"/>
     </row>
@@ -4186,7 +4186,7 @@
         <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00965475140130624</v>
+        <v>0.00959795172690207</v>
       </c>
       <c r="D20"/>
     </row>
@@ -4198,7 +4198,7 @@
         <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D21"/>
     </row>
@@ -4210,7 +4210,7 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D22"/>
     </row>
@@ -4222,7 +4222,7 @@
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00609782626182335</v>
+        <v>0.00606189719778185</v>
       </c>
       <c r="D23"/>
     </row>
@@ -4234,7 +4234,7 @@
         <v>42</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00355692513948289</v>
+        <v>0.00353605452912022</v>
       </c>
       <c r="D24"/>
     </row>
@@ -4246,7 +4246,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00203267884389815</v>
+        <v>0.00202063239926062</v>
       </c>
       <c r="D25"/>
     </row>
@@ -4283,10 +4283,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>29.5596890511849</v>
+        <v>29.5598568310332</v>
       </c>
       <c r="D2" t="n">
-        <v>1.57484095938842</v>
+        <v>1.57499445086972</v>
       </c>
     </row>
     <row r="3">
@@ -4297,10 +4297,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1689234804074</v>
+        <v>18.1673264885753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.432739320612276</v>
+        <v>0.432718841054423</v>
       </c>
     </row>
     <row r="4">
@@ -4311,10 +4311,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>11.2867641756239</v>
+        <v>11.2870459326145</v>
       </c>
       <c r="D4" t="n">
-        <v>7.79747841092047</v>
+        <v>7.79773733744146</v>
       </c>
     </row>
     <row r="5">
@@ -4325,10 +4325,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>8.0097858428954</v>
+        <v>8.01115393796449</v>
       </c>
       <c r="D5" t="n">
-        <v>1.60905995460106</v>
+        <v>1.60936124402573</v>
       </c>
     </row>
     <row r="6">
@@ -4339,10 +4339,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>6.77989306604406</v>
+        <v>6.77881974051897</v>
       </c>
       <c r="D6" t="n">
-        <v>1.16354430973066</v>
+        <v>1.16335433995446</v>
       </c>
     </row>
     <row r="7">
@@ -4353,10 +4353,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>5.00161947931982</v>
+        <v>5.0032033227461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0967029464737107</v>
+        <v>0.0967500459026134</v>
       </c>
     </row>
     <row r="8">
@@ -4367,10 +4367,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>4.17942439810022</v>
+        <v>4.17865556908465</v>
       </c>
       <c r="D8" t="n">
-        <v>0.629474802709262</v>
+        <v>0.629336454614041</v>
       </c>
     </row>
     <row r="9">
@@ -4381,10 +4381,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>3.96557918239868</v>
+        <v>3.96573075921366</v>
       </c>
       <c r="D9" t="n">
-        <v>0.113591911080886</v>
+        <v>0.113586087641846</v>
       </c>
     </row>
     <row r="10">
@@ -4395,10 +4395,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>2.78975080444999</v>
+        <v>2.78941399814897</v>
       </c>
       <c r="D10" t="n">
-        <v>0.237114443555658</v>
+        <v>0.237065455423461</v>
       </c>
     </row>
     <row r="11">
@@ -4409,10 +4409,10 @@
         <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>2.65381557600859</v>
+        <v>2.65389443500849</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10004303459688</v>
+        <v>1.1000766666257</v>
       </c>
     </row>
     <row r="12">
@@ -4423,10 +4423,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>1.54503415439421</v>
+        <v>1.54499986880777</v>
       </c>
       <c r="D12" t="n">
-        <v>0.250650727927502</v>
+        <v>0.250653674269885</v>
       </c>
     </row>
     <row r="13">
@@ -4437,10 +4437,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0631987894026</v>
+        <v>1.06308706922884</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0927383291354896</v>
+        <v>0.0927261331216983</v>
       </c>
     </row>
     <row r="14">
@@ -4451,10 +4451,10 @@
         <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>1.02049527221126</v>
+        <v>1.02077254256731</v>
       </c>
       <c r="D14" t="n">
-        <v>0.138657125616405</v>
+        <v>0.138720194014761</v>
       </c>
     </row>
     <row r="15">
@@ -4465,10 +4465,10 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>0.935661132298646</v>
+        <v>0.93565860860922</v>
       </c>
       <c r="D15" t="n">
-        <v>0.403450995764877</v>
+        <v>0.403441789026877</v>
       </c>
     </row>
     <row r="16">
@@ -4479,10 +4479,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>0.52465053254293</v>
+        <v>0.524886032008783</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0874988293783325</v>
+        <v>0.0875463352201652</v>
       </c>
     </row>
     <row r="17">
@@ -4493,10 +4493,10 @@
         <v>46</v>
       </c>
       <c r="C17" t="n">
-        <v>0.524260671449889</v>
+        <v>0.524152306972405</v>
       </c>
       <c r="D17" t="n">
-        <v>0.323530587624025</v>
+        <v>0.323469312291106</v>
       </c>
     </row>
     <row r="18">
@@ -4507,10 +4507,10 @@
         <v>35</v>
       </c>
       <c r="C18" t="n">
-        <v>0.303872012520068</v>
+        <v>0.303826205899054</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0419851916877287</v>
+        <v>0.0419340104262094</v>
       </c>
     </row>
     <row r="19">
@@ -4521,10 +4521,10 @@
         <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>0.297590307020918</v>
+        <v>0.297553863194058</v>
       </c>
       <c r="D19" t="n">
-        <v>0.105589392066944</v>
+        <v>0.105597733144794</v>
       </c>
     </row>
     <row r="20">
@@ -4535,10 +4535,10 @@
         <v>41</v>
       </c>
       <c r="C20" t="n">
-        <v>0.26521902396207</v>
+        <v>0.26530472662009</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0206940780505517</v>
+        <v>0.0206946981035593</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>0.25487580782696</v>
+        <v>0.254814837259604</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0191447711243624</v>
+        <v>0.0191428227718087</v>
       </c>
     </row>
     <row r="22">
@@ -4563,7 +4563,7 @@
         <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>0.253991756615979</v>
+        <v>0.253949371069562</v>
       </c>
       <c r="D22"/>
     </row>
@@ -4575,10 +4575,10 @@
         <v>30</v>
       </c>
       <c r="C23" t="n">
-        <v>0.173577872758271</v>
+        <v>0.173568969952148</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0241654040245121</v>
+        <v>0.0241653376278085</v>
       </c>
     </row>
     <row r="24">
@@ -4586,26 +4586,26 @@
         <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>0.11370582480294</v>
-      </c>
-      <c r="D24"/>
+        <v>0.113714572470864</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0203644825135999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>0.11370582480294</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.020369505421689</v>
-      </c>
+        <v>0.113712742732618</v>
+      </c>
+      <c r="D25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
@@ -4615,10 +4615,10 @@
         <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0971852321935793</v>
+        <v>0.0971847171625386</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0203933620660771</v>
+        <v>0.0203647318536465</v>
       </c>
     </row>
     <row r="27">
@@ -4629,7 +4629,7 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0741321783585579</v>
+        <v>0.0741080584124175</v>
       </c>
       <c r="D27"/>
     </row>
@@ -4641,7 +4641,7 @@
         <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0222403856410754</v>
+        <v>0.0222331494190234</v>
       </c>
       <c r="D28"/>
     </row>
@@ -4653,7 +4653,7 @@
         <v>50</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0213581647638638</v>
+        <v>0.0213713427054722</v>
       </c>
       <c r="D29"/>
     </row>
